--- a/public/static/定点定价导入模板.xlsx
+++ b/public/static/定点定价导入模板.xlsx
@@ -4,11 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9180"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="定点定价" sheetId="1" r:id="rId1"/>
-    <sheet name="说明" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,11 +36,11 @@
       <rPr>
         <b/>
         <sz val="12"/>
-        <color rgb="FFFFFFFF"/>
+        <color indexed="9"/>
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>产品图号(</t>
+      <t>品名规格(</t>
     </r>
     <r>
       <rPr>
@@ -97,13 +96,10 @@
     </r>
   </si>
   <si>
-    <t>税率(%)</t>
+    <t>税率(税率)</t>
   </si>
   <si>
-    <t>不含税价</t>
-  </si>
-  <si>
-    <t>目标价</t>
+    <t>协议价(不含税)</t>
   </si>
   <si>
     <r>
@@ -114,7 +110,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>有效起始时间(</t>
+      <t>有效时间起(</t>
     </r>
     <r>
       <rPr>
@@ -146,7 +142,7 @@
         <rFont val="宋体"/>
         <charset val="134"/>
       </rPr>
-      <t>有效结束时间(</t>
+      <t>有效时间止(</t>
     </r>
     <r>
       <rPr>
@@ -176,13 +172,13 @@
     <t>1</t>
   </si>
   <si>
+    <t>100</t>
+  </si>
+  <si>
     <t>13</t>
   </si>
   <si>
-    <t xml:space="preserve">说明：
-1、协议价必填，不含税价通过协议价和税率自动计算
-2、税率如果未填写，默认为13%
-</t>
+    <t>88.49</t>
   </si>
 </sst>
 </file>
@@ -195,17 +191,10 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FFC00000"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -218,173 +207,173 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color indexed="8"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -721,19 +710,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -742,153 +740,135 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1424,114 +1404,65 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelRow="1"/>
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="7.11111111111111" customWidth="1"/>
+    <col min="1" max="1" width="7.10833333333333" customWidth="1"/>
     <col min="2" max="2" width="20" customWidth="1"/>
-    <col min="3" max="3" width="24.4444444444444" customWidth="1"/>
+    <col min="3" max="3" width="24.4416666666667" customWidth="1"/>
     <col min="4" max="4" width="13.3333333333333" customWidth="1"/>
-    <col min="5" max="5" width="15.8888888888889" customWidth="1"/>
-    <col min="6" max="6" width="15.7777777777778" customWidth="1"/>
-    <col min="7" max="7" width="22.3333333333333" customWidth="1"/>
-    <col min="8" max="8" width="21.6666666666667" customWidth="1"/>
-    <col min="9" max="9" width="31.2222222222222" customWidth="1"/>
+    <col min="5" max="5" width="21.1083333333333" customWidth="1"/>
+    <col min="6" max="6" width="22.3333333333333" customWidth="1"/>
+    <col min="7" max="7" width="21.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="31.225" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="25" customHeight="1" spans="1:8">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:8">
+      <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:9">
-      <c r="A2" s="5" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="5"/>
+      <c r="E2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:A29"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="131.777777777778" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="96" customHeight="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" ht="25" customHeight="1"/>
-    <row r="3" ht="25" customHeight="1"/>
-    <row r="4" ht="25" customHeight="1"/>
-    <row r="5" ht="25" customHeight="1"/>
-    <row r="6" ht="25" customHeight="1"/>
-    <row r="7" ht="25" customHeight="1"/>
-    <row r="8" ht="25" customHeight="1"/>
-    <row r="9" ht="25" customHeight="1"/>
-    <row r="10" ht="25" customHeight="1"/>
-    <row r="11" ht="25" customHeight="1"/>
-    <row r="12" ht="25" customHeight="1"/>
-    <row r="13" ht="25" customHeight="1"/>
-    <row r="14" ht="25" customHeight="1"/>
-    <row r="15" ht="25" customHeight="1"/>
-    <row r="16" ht="25" customHeight="1"/>
-    <row r="17" ht="25" customHeight="1"/>
-    <row r="18" ht="25" customHeight="1"/>
-    <row r="19" ht="25" customHeight="1"/>
-    <row r="20" ht="25" customHeight="1"/>
-    <row r="21" ht="25" customHeight="1"/>
-    <row r="22" ht="25" customHeight="1"/>
-    <row r="23" ht="25" customHeight="1"/>
-    <row r="24" ht="25" customHeight="1"/>
-    <row r="25" ht="25" customHeight="1"/>
-    <row r="26" ht="25" customHeight="1"/>
-    <row r="27" ht="25" customHeight="1"/>
-    <row r="28" ht="25" customHeight="1"/>
-    <row r="29" ht="25" customHeight="1"/>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
-</worksheet>
 </file>
--- a/public/static/定点定价导入模板.xlsx
+++ b/public/static/定点定价导入模板.xlsx
@@ -96,7 +96,7 @@
     </r>
   </si>
   <si>
-    <t>税率(税率)</t>
+    <t>税率(%)</t>
   </si>
   <si>
     <t>协议价(不含税)</t>
@@ -366,14 +366,14 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
